--- a/recipes/onion-garlic-free-indian/focus-states/06-kerala/excel/kerala-recipes.xlsx
+++ b/recipes/onion-garlic-free-indian/focus-states/06-kerala/excel/kerala-recipes.xlsx
@@ -104,7 +104,7 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="009A3412"/>
-      <sz val="16"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="19">
@@ -259,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -358,6 +358,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="18" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1465,7 +1468,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1477,7 +1480,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cabbage Thoran</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cabbage Thoran</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1487,7 +1490,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Side  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1507,44 +1510,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -1764,38 +1767,204 @@
       <c r="C23" s="46" t="n"/>
       <c r="D23" s="46" t="n"/>
     </row>
-    <row r="24" ht="36" customHeight="1">
+    <row r="24" ht="66" customHeight="1">
       <c r="A24" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B24" s="48" t="inlineStr">
         <is>
-          <t>Temper, cover briefly, mix coconut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C24" s="49" t="n"/>
       <c r="D24" s="49" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Temper, cover briefly, mix coconut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B30" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="n"/>
+      <c r="D30" s="49" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 239  ·  Protein 11 g  ·  Carbs 31 g  ·  Fat 9 g  ·  Fibre 11 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Cabbage Thoran: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="C20:D20"/>
+  <mergeCells count="32">
     <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
     <mergeCell ref="A22:D22"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
-    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -1809,7 +1978,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1821,7 +1990,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Erissery</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Erissery</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1831,7 +2000,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Side  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -1851,44 +2020,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -2090,37 +2259,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Cook pumpkin and peas. Add coconut paste. Temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Cook pumpkin and peas. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Add coconut paste. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 158  ·  Protein 4 g  ·  Carbs 17 g  ·  Fat 9 g  ·  Fibre 5 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Erissery: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2134,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2146,7 +2494,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Beetroot Thoran</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Beetroot Thoran</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2156,7 +2504,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Side  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Side</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2176,44 +2524,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>22 min</t>
+          <t>Prep 10 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -2397,36 +2745,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Stir-fry, coconut.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Stir-fry, coconut. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 167  ·  Protein 3 g  ·  Carbs 16 g  ·  Fat 11 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Beetroot Thoran: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve family-style in a steel bowl. Keep a lid on at the pass so it does not skin. Service temperature: Hot. Allergen label for this dish: Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2440,7 +2941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2452,7 +2953,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Appam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Appam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2462,7 +2963,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Bread  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2482,44 +2983,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>70 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>90 min</t>
+          <t>Prep 70 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -2685,35 +3186,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Ferment, swirl in iron pan, cover 1 minute.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron tawa (not aluminium). Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Ferment, swirl in iron pan, cover 1 minute. Work in Cast-iron tawa (not aluminium). Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 366  ·  Protein 4 g  ·  Carbs 68 g  ·  Fat 9 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Appam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2727,7 +3381,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2739,7 +3393,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Puttu</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Puttu</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2749,7 +3403,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Bread  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -2769,44 +3423,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 15 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -2954,34 +3608,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Layer flour and coconut. Steam 5–7 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Layer flour and coconut. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Steam 5–7 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 206  ·  Protein 3 g  ·  Carbs 33 g  ·  Fat 7 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Puttu: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -2995,7 +3815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3007,7 +3827,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Idiyappam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Idiyappam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3017,7 +3837,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Bread  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Bread</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3037,44 +3857,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 20 min · Cook 10 min</t>
         </is>
       </c>
     </row>
@@ -3222,34 +4042,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Press noodles, steam in steel 5 minutes.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="42" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. For dough, add water gradually; rest covered 10–15 minutes before rolling.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Press noodles, steam in steel 5 minutes. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: bread is cooked through, no wet dough in the centre, light brown spots on the face.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold wrapped in a clean cloth in a covered steel box up to 30 minutes. Refresh on a hot tawa 20 seconds if needed. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 178  ·  Protein 2 g  ·  Carbs 24 g  ·  Fat 8 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Idiyappam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Send to table wrapped. Do not stack in plastic or they sweat. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3263,7 +4236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3275,7 +4248,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Unniyappam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Unniyappam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3285,7 +4258,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Sweet  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3305,44 +4278,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 20 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3526,36 +4499,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Thick batter, fry in ghee wells.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Cast-iron unniyappam pan — not aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Thick batter, fry in ghee wells. Work in Cast-iron unniyappam pan — not aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 436  ·  Protein 4 g  ·  Carbs 72 g  ·  Fat 16 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Unniyappam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3569,7 +4695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3581,7 +4707,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ela Ada</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ela Ada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3591,7 +4717,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Sweet  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3611,44 +4737,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 25 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -3778,33 +4904,186 @@
       <c r="C18" s="46" t="n"/>
       <c r="D18" s="46" t="n"/>
     </row>
-    <row r="19" ht="36" customHeight="1">
+    <row r="19" ht="66" customHeight="1">
       <c r="A19" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B19" s="48" t="inlineStr">
         <is>
-          <t>Spread, fill, fold, steam in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel steamer and steel thali — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C19" s="49" t="n"/>
       <c r="D19" s="49" t="n"/>
     </row>
+    <row r="20" ht="36" customHeight="1">
+      <c r="A20" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="n"/>
+      <c r="D20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="54" customHeight="1">
+      <c r="A21" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B21" s="48" t="inlineStr">
+        <is>
+          <t>Spread, fill, fold, steam in steel. Work in Stainless steel steamer and steel thali — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C21" s="49" t="n"/>
+      <c r="D21" s="49" t="n"/>
+    </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B26" s="22" t="n"/>
+      <c r="C26" s="22" t="n"/>
+      <c r="D26" s="22" t="n"/>
+    </row>
+    <row r="27" ht="36" customHeight="1">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>kcal 320  ·  Protein 4 g  ·  Carbs 41 g  ·  Fat 17 g  ·  Fibre 6 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B27" s="50" t="n"/>
+      <c r="C27" s="50" t="n"/>
+      <c r="D27" s="50" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="48" customHeight="1">
+      <c r="A29" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="26" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="72" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>For Ela Ada: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="64" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="26">
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A26:D26"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -3818,7 +5097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3830,7 +5109,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Sharkara Upperi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Sharkara Upperi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3840,7 +5119,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Sweet  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Sweet</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -3860,44 +5139,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Prep 10 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -4045,34 +5324,187 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Toss chips in thick jaggery syrup in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Toss chips in thick jaggery syrup in steel. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="22" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>kcal 246  ·  Protein 1 g  ·  Carbs 63 g  ·  Fat 0 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B28" s="50" t="n"/>
+      <c r="C28" s="50" t="n"/>
+      <c r="D28" s="50" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+    </row>
+    <row r="30" ht="48" customHeight="1">
+      <c r="A30" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="26" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="72" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>For Sharkara Upperi: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B33" s="52" t="n"/>
+      <c r="C33" s="52" t="n"/>
+      <c r="D33" s="52" t="n"/>
+    </row>
+    <row r="34" ht="64" customHeight="1">
+      <c r="A34" s="12" t="inlineStr">
+        <is>
+          <t>Cut even portions. Garnish with nuts only if the allergen card allows. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B34" s="50" t="n"/>
+      <c r="C34" s="50" t="n"/>
+      <c r="D34" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="27">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4086,7 +5518,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4098,7 +5530,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Palada Payasam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Palada Payasam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4108,7 +5540,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Dessert  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4128,44 +5560,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>55 min</t>
+          <t>Prep 15 min · Cook 40 min</t>
         </is>
       </c>
     </row>
@@ -4331,35 +5763,201 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Reduce milk in steel until beige-pink. Add ada.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Heavy stainless steel milk pot — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Reduce milk in steel until beige-pink. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Add ada. Work in Heavy stainless steel milk pot — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 500  ·  Protein 12 g  ·  Carbs 77 g  ·  Fat 16 g  ·  Fibre 1 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Palada Payasam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4637,7 +6235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4649,7 +6247,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Ada Pradhaman</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Ada Pradhaman</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4659,7 +6257,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Dessert  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4679,44 +6277,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 15 min · Cook 30 min</t>
         </is>
       </c>
     </row>
@@ -4900,36 +6498,215 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Cook ada in jaggery. Coconut milk. Do not boil hard after thick milk.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cook ada in jaggery. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Coconut milk. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Do not boil hard after thick milk. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B28" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="n"/>
+      <c r="D28" s="49" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="31" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 613  ·  Protein 5 g  ·  Carbs 57 g  ·  Fat 42 g  ·  Fibre 9 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Ada Pradhaman: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -4943,7 +6720,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -4955,7 +6732,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Parippu Payasam</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Parippu Payasam</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4965,7 +6742,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Dessert  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Dessert</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -4985,44 +6762,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot or chilled</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 10 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -5188,35 +6965,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook dal, add jaggery and coconut milk.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="42" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook dal, add jaggery and coconut milk. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: mixture leaves the sides of the pan, or milk is thick enough to coat a spoon, or syrup has taken the stated string.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold as the dish is eaten — hot sweets in a bain of hot water, chilled sweets in the fridge. Label date and time. Service: Hot or chilled.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 643  ·  Protein 12 g  ·  Carbs 63 g  ·  Fat 40 g  ·  Fibre 15 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Parippu Payasam: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve in steel or glass bowls. If chilled, take out 5 minutes before the pass. Service temperature: Hot or chilled. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5230,7 +7160,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5242,7 +7172,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Cucumber Kichadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Cucumber Kichadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5252,7 +7182,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Salad  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5272,44 +7202,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Prep 10 min · Cook 5 min</t>
         </is>
       </c>
     </row>
@@ -5475,35 +7405,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="54" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Fold, temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel or glass bowl. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Fold, temper. Work in Steel or glass bowl. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 116  ·  Protein 3 g  ·  Carbs 9 g  ·  Fat 8 g  ·  Fibre 2 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Cucumber Kichadi: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5517,7 +7600,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5529,7 +7612,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pineapple Pachadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pineapple Pachadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5539,7 +7622,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Salad  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5559,44 +7642,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>27 min</t>
+          <t>Prep 15 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -5780,36 +7863,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Cook pineapple, add paste and yogurt off the boil.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cook pineapple, add paste and yogurt off the boil. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 163  ·  Protein 4 g  ·  Carbs 15 g  ·  Fat 10 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Pineapple Pachadi: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -5823,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5835,7 +8071,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Beetroot Pachadi</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Beetroot Pachadi</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5845,7 +8081,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Salad  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Salad</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -5865,44 +8101,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>12 min</t>
+          <t>Cold</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>27 min</t>
+          <t>Prep 15 min · Cook 12 min</t>
         </is>
       </c>
     </row>
@@ -6068,35 +8304,188 @@
       <c r="C20" s="46" t="n"/>
       <c r="D20" s="46" t="n"/>
     </row>
-    <row r="21" ht="36" customHeight="1">
+    <row r="21" ht="66" customHeight="1">
       <c r="A21" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B21" s="48" t="inlineStr">
         <is>
-          <t>Cook beet, fold coconut-yogurt, temper.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C21" s="49" t="n"/>
       <c r="D21" s="49" t="n"/>
     </row>
+    <row r="22" ht="36" customHeight="1">
+      <c r="A22" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C22" s="31" t="n"/>
+      <c r="D22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="48" t="inlineStr">
+        <is>
+          <t>Cook beet, fold coconut-yogurt, temper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="49" t="n"/>
+      <c r="D23" s="49" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables stay crisp; dressing coats evenly; seasoning is bright, not flat.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Hold chilled, covered, up to 2 hours. Stir before service. Discard if it weeps heavily or smells sour beyond yogurt character. Service: Cold.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 177  ·  Protein 5 g  ·  Carbs 17 g  ·  Fat 11 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Mustard · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Beetroot Pachadi: squeeze wet vegetables dry or the bowl weeps on the pass. Season slightly higher than you think — cold dulls salt. No onion, no garlic, no allium garnish. Use steel or glass, never aluminium. Dress at the last minute. Verify dahi and spice labels.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Dress at the last minute. Toss at the pass, do not send a wet bowl. Service temperature: Cold. Allergen label for this dish: Milk; Mustard; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A19:D19"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9443,7 +11832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9455,7 +11844,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Pazham Pori</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Pazham Pori</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9465,7 +11854,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Starter  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9485,44 +11874,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -9706,36 +12095,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Batter, fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="54" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Batter, fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 575  ·  Protein 10 g  ·  Carbs 116 g  ·  Fat 8 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Pazham Pori: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -9749,7 +12291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9761,7 +12303,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Parippu Vada</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Parippu Vada</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9771,7 +12313,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Starter  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -9791,44 +12333,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 20 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10030,37 +12572,203 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="36" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Shape, fry in steel.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="36" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Steel kadhai for frying — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Shape, fry in steel. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="n"/>
+      <c r="C31" s="22" t="n"/>
+      <c r="D31" s="22" t="n"/>
+    </row>
+    <row r="32" ht="36" customHeight="1">
+      <c r="A32" s="12" t="inlineStr">
+        <is>
+          <t>kcal 160  ·  Protein 5 g  ·  Carbs 17 g  ·  Fat 9 g  ·  Fibre 4 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B32" s="50" t="n"/>
+      <c r="C32" s="50" t="n"/>
+      <c r="D32" s="50" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="48" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+    </row>
+    <row r="36" ht="72" customHeight="1">
+      <c r="A36" s="25" t="inlineStr">
+        <is>
+          <t>For Parippu Vada: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="26" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B37" s="52" t="n"/>
+      <c r="C37" s="52" t="n"/>
+      <c r="D37" s="52" t="n"/>
+    </row>
+    <row r="38" ht="64" customHeight="1">
+      <c r="A38" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B38" s="50" t="n"/>
+      <c r="C38" s="50" t="n"/>
+      <c r="D38" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="31">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10074,7 +12782,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D20"/>
+  <dimension ref="A1:D35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10086,7 +12794,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Upperi Banana Chips</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Upperi Banana Chips</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10096,7 +12804,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Starter  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Starter</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10116,44 +12824,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>10 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Prep 10 min · Cook 15 min</t>
         </is>
       </c>
     </row>
@@ -10301,34 +13009,200 @@
       <c r="C19" s="46" t="n"/>
       <c r="D19" s="46" t="n"/>
     </row>
-    <row r="20" ht="36" customHeight="1">
+    <row r="20" ht="66" customHeight="1">
       <c r="A20" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B20" s="48" t="inlineStr">
         <is>
-          <t>Fry in coconut oil in a steel kadhai. Salt.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Steel kadhai for frying — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C20" s="49" t="n"/>
       <c r="D20" s="49" t="n"/>
     </row>
+    <row r="21" ht="36" customHeight="1">
+      <c r="A21" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="54" customHeight="1">
+      <c r="A22" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="48" t="inlineStr">
+        <is>
+          <t>Fry in coconut oil in a steel kadhai. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="n"/>
+      <c r="D22" s="49" t="n"/>
+    </row>
+    <row r="23" ht="54" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Salt. Work in Steel kadhai for frying — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Doneness: crust or crumb is set, centre is hot, no raw flour or potato taste. Drain on a steel rack, not paper in the fryer basket.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="n"/>
+      <c r="C28" s="22" t="n"/>
+      <c r="D28" s="22" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>kcal 114  ·  Protein 1 g  ·  Carbs 24 g  ·  Fat 3 g  ·  Fibre 3 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B29" s="50" t="n"/>
+      <c r="C29" s="50" t="n"/>
+      <c r="D29" s="50" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+    </row>
+    <row r="31" ht="48" customHeight="1">
+      <c r="A31" s="25" t="inlineStr">
+        <is>
+          <t>None identified in this spec — still verify hing brand (many contain wheat) and spice blends.</t>
+        </is>
+      </c>
+      <c r="B31" s="26" t="n"/>
+      <c r="C31" s="26" t="n"/>
+      <c r="D31" s="26" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+    </row>
+    <row r="33" ht="72" customHeight="1">
+      <c r="A33" s="25" t="inlineStr">
+        <is>
+          <t>For Upperi Banana Chips: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="26" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B34" s="52" t="n"/>
+      <c r="C34" s="52" t="n"/>
+      <c r="D34" s="52" t="n"/>
+    </row>
+    <row r="35" ht="64" customHeight="1">
+      <c r="A35" s="12" t="inlineStr">
+        <is>
+          <t>Serve immediately while crisp or hot. Offer a chutney or raita that is also onion-garlic free. Service temperature: Hot. Allergen label for this dish: None identified in this spec — still verify hing brand (many contain wheat) and spice blends. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B35" s="50" t="n"/>
+      <c r="C35" s="50" t="n"/>
+      <c r="D35" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="28">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B19:D19"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
     <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C14:D14"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="B20:D20"/>
+    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10342,7 +13216,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10354,7 +13228,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Avial</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Avial</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10364,7 +13238,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Main  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10384,44 +13258,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>Prep 20 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -10605,36 +13479,189 @@
       <c r="C21" s="46" t="n"/>
       <c r="D21" s="46" t="n"/>
     </row>
-    <row r="22" ht="36" customHeight="1">
+    <row r="22" ht="66" customHeight="1">
       <c r="A22" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B22" s="48" t="inlineStr">
         <is>
-          <t>Cook veg, add coconut, fold yogurt off the boil, coconut oil.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C22" s="49" t="n"/>
       <c r="D22" s="49" t="n"/>
     </row>
+    <row r="23" ht="36" customHeight="1">
+      <c r="A23" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together.</t>
+        </is>
+      </c>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="31" t="n"/>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B24" s="48" t="inlineStr">
+        <is>
+          <t>Cook veg, add coconut, fold yogurt off the boil, coconut oil. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="n"/>
+      <c r="D24" s="49" t="n"/>
+    </row>
+    <row r="25" ht="42" customHeight="1">
+      <c r="A25" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="42" customHeight="1">
+      <c r="A26" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B26" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="n"/>
+      <c r="D26" s="49" t="n"/>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="31" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="n"/>
+      <c r="C29" s="22" t="n"/>
+      <c r="D29" s="22" t="n"/>
+    </row>
+    <row r="30" ht="36" customHeight="1">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>kcal 189  ·  Protein 4 g  ·  Carbs 22 g  ·  Fat 11 g  ·  Fibre 7 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B30" s="50" t="n"/>
+      <c r="C30" s="50" t="n"/>
+      <c r="D30" s="50" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+    </row>
+    <row r="32" ht="48" customHeight="1">
+      <c r="A32" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="26" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+    </row>
+    <row r="34" ht="72" customHeight="1">
+      <c r="A34" s="25" t="inlineStr">
+        <is>
+          <t>For Avial: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder. Bring yogurt to a simmer gently and stir; a rolling boil can split it.</t>
+        </is>
+      </c>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="26" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B35" s="52" t="n"/>
+      <c r="C35" s="52" t="n"/>
+      <c r="D35" s="52" t="n"/>
+    </row>
+    <row r="36" ht="64" customHeight="1">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B36" s="50" t="n"/>
+      <c r="C36" s="50" t="n"/>
+      <c r="D36" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="29">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A29:D29"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="B21:D21"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10648,7 +13675,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10660,7 +13687,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Olan</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Olan</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10670,7 +13697,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Main  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -10690,44 +13717,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>35 min</t>
+          <t>Prep 15 min · Cook 20 min</t>
         </is>
       </c>
     </row>
@@ -10929,37 +13956,216 @@
       <c r="C22" s="46" t="n"/>
       <c r="D22" s="46" t="n"/>
     </row>
-    <row r="23" ht="42" customHeight="1">
+    <row r="23" ht="66" customHeight="1">
       <c r="A23" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B23" s="48" t="inlineStr">
         <is>
-          <t>Simmer gourd and peas in thin milk. Finish thick milk and curry leaves. No allium.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C23" s="49" t="n"/>
       <c r="D23" s="49" t="n"/>
     </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n"/>
+      <c r="D24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="54" customHeight="1">
+      <c r="A25" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B25" s="48" t="inlineStr">
+        <is>
+          <t>Simmer gourd and peas in thin milk. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C25" s="49" t="n"/>
+      <c r="D25" s="49" t="n"/>
+    </row>
+    <row r="26" ht="54" customHeight="1">
+      <c r="A26" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Finish thick milk and curry leaves. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n"/>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="54" customHeight="1">
+      <c r="A27" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B27" s="48" t="inlineStr">
+        <is>
+          <t>No allium. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C27" s="49" t="n"/>
+      <c r="D27" s="49" t="n"/>
+    </row>
+    <row r="28" ht="42" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="42" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B32" s="22" t="n"/>
+      <c r="C32" s="22" t="n"/>
+      <c r="D32" s="22" t="n"/>
+    </row>
+    <row r="33" ht="36" customHeight="1">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>kcal 533  ·  Protein 10 g  ·  Carbs 41 g  ·  Fat 39 g  ·  Fibre 16 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B33" s="50" t="n"/>
+      <c r="C33" s="50" t="n"/>
+      <c r="D33" s="50" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+    </row>
+    <row r="35" ht="48" customHeight="1">
+      <c r="A35" s="25" t="inlineStr">
+        <is>
+          <t>Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="26" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n"/>
+      <c r="C36" s="6" t="n"/>
+      <c r="D36" s="6" t="n"/>
+    </row>
+    <row r="37" ht="72" customHeight="1">
+      <c r="A37" s="25" t="inlineStr">
+        <is>
+          <t>For Olan: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="26" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B38" s="52" t="n"/>
+      <c r="C38" s="52" t="n"/>
+      <c r="D38" s="52" t="n"/>
+    </row>
+    <row r="39" ht="64" customHeight="1">
+      <c r="A39" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B39" s="50" t="n"/>
+      <c r="C39" s="50" t="n"/>
+      <c r="D39" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="32">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A35:D35"/>
+    <mergeCell ref="A38:D38"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A39:D39"/>
+    <mergeCell ref="B30:D30"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="B26:D26"/>
+    <mergeCell ref="B25:D25"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="A37:D37"/>
     <mergeCell ref="B22:D22"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="A21:D21"/>
-    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="C17:D17"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A32:D32"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
@@ -10973,7 +14179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10985,7 +14191,7 @@
     <row r="1" ht="32" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>RECIPE CARD  ·  Vegetable Stew</t>
+          <t>Parslia Kitchen OS · RECIPE CARD · Vegetable Stew</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10995,7 +14201,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Kerala kitchen  ·  Main  ·  Kerala sadya kitchen</t>
+          <t>Pure Prasad · No onion · No garlic · No eggs · No meat · No fish  ·  Kerala  ·  Main</t>
         </is>
       </c>
       <c r="B2" s="4" t="n"/>
@@ -11015,44 +14221,44 @@
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="39" t="inlineStr">
         <is>
-          <t>Serves</t>
+          <t>YIELD</t>
         </is>
       </c>
       <c r="B5" s="39" t="inlineStr">
         <is>
-          <t>Prep</t>
+          <t>PORTION</t>
         </is>
       </c>
       <c r="C5" s="39" t="inlineStr">
         <is>
-          <t>Cook</t>
+          <t>SERVICE</t>
         </is>
       </c>
       <c r="D5" s="39" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>TIME</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
       <c r="A6" s="40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>4 portions</t>
         </is>
       </c>
       <c r="B6" s="40" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 portion</t>
         </is>
       </c>
       <c r="C6" s="40" t="inlineStr">
         <is>
-          <t>25 min</t>
+          <t>Hot</t>
         </is>
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>40 min</t>
+          <t>Prep 15 min · Cook 25 min</t>
         </is>
       </c>
     </row>
@@ -11326,41 +14532,220 @@
       <c r="C26" s="46" t="n"/>
       <c r="D26" s="46" t="n"/>
     </row>
-    <row r="27" ht="42" customHeight="1">
+    <row r="27" ht="66" customHeight="1">
       <c r="A27" s="47" t="n">
         <v>1</v>
       </c>
       <c r="B27" s="48" t="inlineStr">
         <is>
-          <t>Simmer veg in thin milk with ginger and pepper. Thick milk at the end.</t>
+          <t>Mise en place. Weigh every ingredient on this card for 4 portions. Set Stainless steel kadhai or saucepan — never aluminium. Wash produce. Confirm spice blends have no onion or garlic powder. No onion, no garlic, no aluminium.</t>
         </is>
       </c>
       <c r="C27" s="49" t="n"/>
       <c r="D27" s="49" t="n"/>
     </row>
+    <row r="28" ht="66" customHeight="1">
+      <c r="A28" s="32" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>Cut vegetables to even size so they cook together. If using potato, cook until tender, drain, and steam-dry so the mix is not wet. Use a heavy stainless steel milk pot. Acidic or milk dishes must never touch aluminium.</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n"/>
+    </row>
+    <row r="29" ht="54" customHeight="1">
+      <c r="A29" s="47" t="n">
+        <v>3</v>
+      </c>
+      <c r="B29" s="48" t="inlineStr">
+        <is>
+          <t>Heat fat in Stainless steel kadhai or saucepan — never aluminium on medium. Bloom hing 20–30 seconds until fragrant — this is the onion-garlic stand-in. Do not burn it.</t>
+        </is>
+      </c>
+      <c r="C29" s="49" t="n"/>
+      <c r="D29" s="49" t="n"/>
+    </row>
+    <row r="30" ht="66" customHeight="1">
+      <c r="A30" s="32" t="n">
+        <v>4</v>
+      </c>
+      <c r="B30" s="30" t="inlineStr">
+        <is>
+          <t>Simmer veg in thin milk with ginger and pepper. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+    </row>
+    <row r="31" ht="54" customHeight="1">
+      <c r="A31" s="47" t="n">
+        <v>5</v>
+      </c>
+      <c r="B31" s="48" t="inlineStr">
+        <is>
+          <t>Thick milk at the end. Work in Stainless steel kadhai or saucepan — never aluminium. Cook to the doneness below, tasting salt at the end. Do not add onion, garlic or aluminium cookware.</t>
+        </is>
+      </c>
+      <c r="C31" s="49" t="n"/>
+      <c r="D31" s="49" t="n"/>
+    </row>
+    <row r="32" ht="42" customHeight="1">
+      <c r="A32" s="32" t="n">
+        <v>6</v>
+      </c>
+      <c r="B32" s="30" t="inlineStr">
+        <is>
+          <t>Doneness: vegetables yield to a knife, gravy coats a spoon, salt is balanced. Rest 2 minutes off the heat so seasoning settles.</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="n"/>
+      <c r="D32" s="31" t="n"/>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="47" t="n">
+        <v>7</v>
+      </c>
+      <c r="B33" s="48" t="inlineStr">
+        <is>
+          <t>Taste and adjust salt, lemon or chilli only — do not add onion or garlic at the finish. Garnish as listed. Yield is 4 portions.</t>
+        </is>
+      </c>
+      <c r="C33" s="49" t="n"/>
+      <c r="D33" s="49" t="n"/>
+    </row>
+    <row r="34" ht="42" customHeight="1">
+      <c r="A34" s="32" t="n">
+        <v>8</v>
+      </c>
+      <c r="B34" s="30" t="inlineStr">
+        <is>
+          <t>Hold hot above 63 C if the pass is delayed, or cool quickly and reheat once only to piping hot. Do not hold in aluminium. Service: Hot.</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n"/>
+      <c r="D34" s="31" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="21" t="inlineStr">
+        <is>
+          <t>Nutrition per portion</t>
+        </is>
+      </c>
+      <c r="B36" s="22" t="n"/>
+      <c r="C36" s="22" t="n"/>
+      <c r="D36" s="22" t="n"/>
+    </row>
+    <row r="37" ht="36" customHeight="1">
+      <c r="A37" s="12" t="inlineStr">
+        <is>
+          <t>kcal 695  ·  Protein 20 g  ·  Carbs 77 g  ·  Fat 37 g  ·  Fibre 24 g. Nutrition is a kitchen estimate from typical produce values, not a laboratory analysis.</t>
+        </is>
+      </c>
+      <c r="B37" s="50" t="n"/>
+      <c r="C37" s="50" t="n"/>
+      <c r="D37" s="50" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="inlineStr">
+        <is>
+          <t>Allergens</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n"/>
+    </row>
+    <row r="39" ht="48" customHeight="1">
+      <c r="A39" s="25" t="inlineStr">
+        <is>
+          <t>Gluten (wheat) · Milk · Always verify labels; this card is a kitchen estimate, not a lab certificate.</t>
+        </is>
+      </c>
+      <c r="B39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="26" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>Chef notes</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+    </row>
+    <row r="41" ht="72" customHeight="1">
+      <c r="A41" s="25" t="inlineStr">
+        <is>
+          <t>For Vegetable Stew: keep the mix slightly drier than you think; wet mixes split or go greasy. Bloom hing in hot fat 20–30 seconds; raw hing tastes medicinal. Commercial hing is often cut with wheat flour — use a gluten-free hing if you must mark Gluten Free. Never cook tomato, tamarind, lemon, yogurt or milk in aluminium; use stainless steel, iron, clay or glass. Spice blends: read the packet. Many garam masalas hide onion or garlic powder.</t>
+        </is>
+      </c>
+      <c r="B41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="26" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="51" t="inlineStr">
+        <is>
+          <t>Service notes</t>
+        </is>
+      </c>
+      <c r="B42" s="52" t="n"/>
+      <c r="C42" s="52" t="n"/>
+      <c r="D42" s="52" t="n"/>
+    </row>
+    <row r="43" ht="64" customHeight="1">
+      <c r="A43" s="12" t="inlineStr">
+        <is>
+          <t>Plate with bread or rice from the same kitchen card. Sauce should nap, not flood. Service temperature: Hot. Allergen label for this dish: Gluten (wheat); Milk; Always verify labels; this card is a kitchen estimate, not a lab certificate. State clearly: vegetarian, no onion, no garlic, no eggs, no meat, no fish. Nutrition on this card is an estimate for 1 portion of 4.</t>
+        </is>
+      </c>
+      <c r="B43" s="50" t="n"/>
+      <c r="C43" s="50" t="n"/>
+      <c r="D43" s="50" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="36">
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="C15:D15"/>
+    <mergeCell ref="A38:D38"/>
     <mergeCell ref="C14:D14"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="B29:D29"/>
+    <mergeCell ref="B34:D34"/>
     <mergeCell ref="C20:D20"/>
+    <mergeCell ref="B28:D28"/>
     <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A40:D40"/>
     <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
+    <mergeCell ref="B30:D30"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A36:D36"/>
+    <mergeCell ref="B33:D33"/>
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
+    <mergeCell ref="B32:D32"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A41:D41"/>
     <mergeCell ref="C17:D17"/>
     <mergeCell ref="C23:D23"/>
+    <mergeCell ref="A37:D37"/>
+    <mergeCell ref="B31:D31"/>
     <mergeCell ref="A3:D3"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="B27:D27"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
     <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A42:D42"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
